--- a/data/project_data.xlsx
+++ b/data/project_data.xlsx
@@ -542,7 +542,7 @@
     <t xml:space="preserve">ΚΑΤΑΣΚΕΥΗ ΝΕΑΣ ΔΙΠΛΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΔΙΑΚΟΠΤΟ-ΡΟΔΟΔΑΦΝΗ, ΦΑΣΗ Β'  </t>
   </si>
   <si>
-    <t>ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
+    <t>ΕΠ-ΥΜΕΠΕΡΑΑ 2014-2020 (Ημιτελείς πράξεις)</t>
   </si>
   <si>
     <t>Η πράξη αφορά στην ολοκλήρωση της κατασκευής των έργων υποδομής και επιδομής σιδηροδρομικής γραμμής με σηματοδότηση, τηλεδιοίκηση και τηλεπικοινωνίες στο τμήμα Διακοπτό-Ροδοδάφνη μήκους 16χλμ περίπου.</t>
